--- a/mistral_translate_work/split_by_prompt/excel/name_title/lang_multi_text/lang_multi_text__name_title__part_0048.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/name_title/lang_multi_text/lang_multi_text__name_title__part_0048.xlsx
@@ -1274,7 +1274,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>*******************</t>
+          <t>Tần số của ta... đang dao động...</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>*******************************</t>
+          <t>********************************</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -1904,7 +1904,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>*******************</t>
+          <t>Tần số của ta... đang dao động...</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -3164,7 +3164,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>*******************************</t>
+          <t>********************************</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -4004,8 +4004,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>************************************************
-```</t>
+          <t>************************************************</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -4775,7 +4774,7 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>*********</t>
+          <t>* * * * * * * * *</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
@@ -6035,7 +6034,7 @@
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>***********</t>
+          <t>* * * * * * * * * * *</t>
         </is>
       </c>
       <c r="N80" t="inlineStr">
@@ -7505,8 +7504,7 @@
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>********************************************************************************
-```</t>
+          <t>********************************************************************************</t>
         </is>
       </c>
       <c r="N101" t="inlineStr">
@@ -7646,7 +7644,7 @@
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>********</t>
+          <t>* * * * * * * *</t>
         </is>
       </c>
       <c r="N103" t="inlineStr">
@@ -8486,7 +8484,7 @@
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>********</t>
+          <t>* * * * * * * *</t>
         </is>
       </c>
       <c r="N115" t="inlineStr">
@@ -8766,7 +8764,7 @@
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>********</t>
+          <t>* * * * * * * *</t>
         </is>
       </c>
       <c r="N119" t="inlineStr">
@@ -9046,7 +9044,7 @@
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t>*******************************</t>
+          <t>********************************</t>
         </is>
       </c>
       <c r="N123" t="inlineStr">
@@ -9256,8 +9254,7 @@
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>**************************************************
-```</t>
+          <t>**************************************************</t>
         </is>
       </c>
       <c r="N126" t="inlineStr">
@@ -9887,7 +9884,7 @@
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t>****</t>
+          <t>*******</t>
         </is>
       </c>
       <c r="N135" t="inlineStr">
@@ -10307,7 +10304,7 @@
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>******************</t>
+          <t>Chúng ta đang ở đâu vậy...?</t>
         </is>
       </c>
       <c r="N141" t="inlineStr">
@@ -10447,7 +10444,7 @@
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t>***********</t>
+          <t>* * * * * * * * * * *</t>
         </is>
       </c>
       <c r="N143" t="inlineStr">
@@ -11007,8 +11004,7 @@
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t>**************************************************************************************
-```</t>
+          <t>**************************************************************************************</t>
         </is>
       </c>
       <c r="N151" t="inlineStr">
@@ -11568,7 +11564,7 @@
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t>***********************************************************</t>
+          <t>*********************************************************</t>
         </is>
       </c>
       <c r="N159" t="inlineStr">
@@ -11988,7 +11984,7 @@
       </c>
       <c r="M165" t="inlineStr">
         <is>
-          <t>************</t>
+          <t>* * * * * * * * * * * *</t>
         </is>
       </c>
       <c r="N165" t="inlineStr">
@@ -12548,7 +12544,7 @@
       </c>
       <c r="M173" t="inlineStr">
         <is>
-          <t>************</t>
+          <t>* * * * * * * * * * * *</t>
         </is>
       </c>
       <c r="N173" t="inlineStr">
@@ -13598,7 +13594,7 @@
       </c>
       <c r="M188" t="inlineStr">
         <is>
-          <t>À—À— (*Tiếng kêu khẳng định*)</t>
+          <t>Á—Á— (*Tiếng kêu khẳng định*)</t>
         </is>
       </c>
       <c r="N188" t="inlineStr">
@@ -13668,7 +13664,7 @@
       </c>
       <c r="M189" t="inlineStr">
         <is>
-          <t>Gửi tất cả các nhà nghiên cứu và sinh viên tham gia hoạt động tại Đồng Bằng Dimmr:</t>
+          <t>Gửi tất cả các nhà nghiên cứu và học viên tham gia hoạt động tại Đồng Bằng Dimmr:</t>
         </is>
       </c>
       <c r="N189" t="inlineStr">
@@ -13738,7 +13734,7 @@
       </c>
       <c r="M190" t="inlineStr">
         <is>
-          <t>Một thời gian sau</t>
+          <t>Một khoảng thời gian sau đó</t>
         </is>
       </c>
       <c r="N190" t="inlineStr">
@@ -13808,7 +13804,7 @@
       </c>
       <c r="M191" t="inlineStr">
         <is>
-          <t>Một thời gian sau</t>
+          <t>Một khoảng thời gian sau đó</t>
         </is>
       </c>
       <c r="N191" t="inlineStr">
@@ -13878,7 +13874,7 @@
       </c>
       <c r="M192" t="inlineStr">
         <is>
-          <t>Bạn bè đã offline</t>
+          <t>Bạn bè đã ngoại tuyến</t>
         </is>
       </c>
       <c r="N192" t="inlineStr">
@@ -13948,7 +13944,7 @@
       </c>
       <c r="M193" t="inlineStr">
         <is>
-          <t>Bạn bè đã offline</t>
+          <t>Bạn bè đã ngoại tuyến</t>
         </is>
       </c>
       <c r="N193" t="inlineStr">
@@ -14018,7 +14014,7 @@
       </c>
       <c r="M194" t="inlineStr">
         <is>
-          <t>Bạn bè đã offline</t>
+          <t>Bạn bè đã ngoại tuyến</t>
         </is>
       </c>
       <c r="N194" t="inlineStr">
@@ -14088,7 +14084,7 @@
       </c>
       <c r="M195" t="inlineStr">
         <is>
-          <t>Đã kết nối</t>
+          <t>Đã kết nối thành công</t>
         </is>
       </c>
       <c r="N195" t="inlineStr">
@@ -14158,7 +14154,7 @@
       </c>
       <c r="M196" t="inlineStr">
         <is>
-          <t>(Đưa khoản thanh toán)</t>
+          <t>(Đưa khoản thanh toán đây.)</t>
         </is>
       </c>
       <c r="N196" t="inlineStr">
@@ -14228,7 +14224,7 @@
       </c>
       <c r="M197" t="inlineStr">
         <is>
-          <t>Một thời gian sau</t>
+          <t>Một khoảng thời gian sau đó</t>
         </is>
       </c>
       <c r="N197" t="inlineStr">
@@ -14298,7 +14294,7 @@
       </c>
       <c r="M198" t="inlineStr">
         <is>
-          <t>Actually, we just wanted to—</t>
+          <t>Thực ra, chúng tôi chỉ muốn—</t>
         </is>
       </c>
       <c r="N198" t="inlineStr">
@@ -14368,7 +14364,7 @@
       </c>
       <c r="M199" t="inlineStr">
         <is>
-          <t>Nhưng khi quá trình ghi âm tiếp tục, sự lo lắng lại ùa về…</t>
+          <t>Nhưng càng ghi âm lâu, nỗi lo lắng lại dần quay trở lại…</t>
         </is>
       </c>
       <c r="N199" t="inlineStr">
@@ -14788,7 +14784,7 @@
       </c>
       <c r="M205" t="inlineStr">
         <is>
-          <t>Tin nhắn cuối cùng truyền đi là: ·—· · — ·—· · ·— —</t>
+          <t>Tin nhắn cuối cùng nó truyền đi là: ·—· · — ·—· · ·— —</t>
         </is>
       </c>
       <c r="N205" t="inlineStr">
@@ -14998,7 +14994,7 @@
       </c>
       <c r="M208" t="inlineStr">
         <is>
-          <t>Honk honk♪</t>
+          <t>Hú hí♪</t>
         </is>
       </c>
       <c r="N208" t="inlineStr">
@@ -15068,7 +15064,7 @@
       </c>
       <c r="M209" t="inlineStr">
         <is>
-          <t>Honk honk♪</t>
+          <t>Hú hí♪</t>
         </is>
       </c>
       <c r="N209" t="inlineStr">
@@ -15208,7 +15204,7 @@
       </c>
       <c r="M211" t="inlineStr">
         <is>
-          <t>*******************</t>
+          <t>Tần số của ta... đang dao động...</t>
         </is>
       </c>
       <c r="N211" t="inlineStr">
@@ -15278,7 +15274,7 @@
       </c>
       <c r="M212" t="inlineStr">
         <is>
-          <t>**********</t>
+          <t>* * * * * * * * * *</t>
         </is>
       </c>
       <c r="N212" t="inlineStr">
@@ -15488,7 +15484,7 @@
       </c>
       <c r="M215" t="inlineStr">
         <is>
-          <t>*******</t>
+          <t>********</t>
         </is>
       </c>
       <c r="N215" t="inlineStr">
@@ -15698,7 +15694,7 @@
       </c>
       <c r="M218" t="inlineStr">
         <is>
-          <t>************</t>
+          <t>* * * * * * * * * * * *</t>
         </is>
       </c>
       <c r="N218" t="inlineStr">
@@ -15838,7 +15834,7 @@
       </c>
       <c r="M220" t="inlineStr">
         <is>
-          <t>*******************</t>
+          <t>Tần số của ta... đang dao động...</t>
         </is>
       </c>
       <c r="N220" t="inlineStr">
@@ -16398,7 +16394,7 @@
       </c>
       <c r="M228" t="inlineStr">
         <is>
-          <t>**********</t>
+          <t>* * * * * * * * * *</t>
         </is>
       </c>
       <c r="N228" t="inlineStr">
@@ -17168,7 +17164,7 @@
       </c>
       <c r="M239" t="inlineStr">
         <is>
-          <t>***********</t>
+          <t>* * * * * * * * * * *</t>
         </is>
       </c>
       <c r="N239" t="inlineStr">
@@ -17658,7 +17654,7 @@
       </c>
       <c r="M246" t="inlineStr">
         <is>
-          <t>******************</t>
+          <t>Chúng ta đang ở đâu vậy...?</t>
         </is>
       </c>
       <c r="N246" t="inlineStr">
@@ -17938,7 +17934,7 @@
       </c>
       <c r="M250" t="inlineStr">
         <is>
-          <t>Chuluu (*Âm thanh xác nhận*)</t>
+          <t>Chuluu (*Âm thanh đồng ý*)</t>
         </is>
       </c>
       <c r="N250" t="inlineStr">
@@ -18008,7 +18004,7 @@
       </c>
       <c r="M251" t="inlineStr">
         <is>
-          <t>Chu chu chu chu chu chu (*Âm thanh bị hạ thân nhiệt*)</t>
+          <t>Chít chít chít chít chít (*Tiếng run lập cập vì lạnh*)</t>
         </is>
       </c>
       <c r="N251" t="inlineStr">
@@ -18078,7 +18074,7 @@
       </c>
       <c r="M252" t="inlineStr">
         <is>
-          <t>Chuu, chuu chuu chuuluu (*Âm thanh xác nhận*)</t>
+          <t>Chít, chít chít luuu (*Âm thanh đồng ý*)</t>
         </is>
       </c>
       <c r="N252" t="inlineStr">
@@ -18148,7 +18144,7 @@
       </c>
       <c r="M253" t="inlineStr">
         <is>
-          <t>Chuu—</t>
+          <t>Chùù—</t>
         </is>
       </c>
       <c r="N253" t="inlineStr">
@@ -19408,7 +19404,7 @@
       </c>
       <c r="M271" t="inlineStr">
         <is>
-          <t>**********</t>
+          <t>* * * * * * * * * *</t>
         </is>
       </c>
       <c r="N271" t="inlineStr">
@@ -19548,7 +19544,7 @@
       </c>
       <c r="M273" t="inlineStr">
         <is>
-          <t>*******************************</t>
+          <t>********************************</t>
         </is>
       </c>
       <c r="N273" t="inlineStr">
@@ -19828,7 +19824,7 @@
       </c>
       <c r="M277" t="inlineStr">
         <is>
-          <t>*******</t>
+          <t>********</t>
         </is>
       </c>
       <c r="N277" t="inlineStr">
@@ -19898,8 +19894,7 @@
       </c>
       <c r="M278" t="inlineStr">
         <is>
-          <t>************************************************
-```</t>
+          <t>************************************************</t>
         </is>
       </c>
       <c r="N278" t="inlineStr">
@@ -21649,7 +21644,7 @@
       </c>
       <c r="M303" t="inlineStr">
         <is>
-          <t>***********</t>
+          <t>* * * * * * * * * * *</t>
         </is>
       </c>
       <c r="N303" t="inlineStr">
@@ -22069,7 +22064,7 @@
       </c>
       <c r="M309" t="inlineStr">
         <is>
-          <t>*******************************</t>
+          <t>********************************</t>
         </is>
       </c>
       <c r="N309" t="inlineStr">
@@ -23399,7 +23394,7 @@
       </c>
       <c r="M328" t="inlineStr">
         <is>
-          <t>Về những điều ước bị tha hóa…</t>
+          <t>Về những điều ước bị tha hóa ấy...</t>
         </is>
       </c>
       <c r="N328" t="inlineStr">
@@ -24029,7 +24024,7 @@
       </c>
       <c r="M337" t="inlineStr">
         <is>
-          <t>Kiểm tra Terminal bị hỏng</t>
+          <t>Kiểm tra Thiết bị đầu cuối bị hỏng</t>
         </is>
       </c>
       <c r="N337" t="inlineStr">
@@ -24239,7 +24234,7 @@
       </c>
       <c r="M340" t="inlineStr">
         <is>
-          <t>Tôi chân thành dâng tặng ngài—</t>
+          <t>Tớ chân thành...</t>
         </is>
       </c>
       <c r="N340" t="inlineStr">
@@ -24309,7 +24304,7 @@
       </c>
       <c r="M341" t="inlineStr">
         <is>
-          <t>Ôi, tình yêu dấu nhất của tôi—</t>
+          <t>Ôi, tình yêu của đời anh—</t>
         </is>
       </c>
       <c r="N341" t="inlineStr">
@@ -24379,7 +24374,7 @@
       </c>
       <c r="M342" t="inlineStr">
         <is>
-          <t>In legends</t>
+          <t>Trong truyền thuyết</t>
         </is>
       </c>
       <c r="N342" t="inlineStr">
@@ -24449,7 +24444,7 @@
       </c>
       <c r="M343" t="inlineStr">
         <is>
-          <t>Cetus the Tidebreaker dẫn dắt những con tàu và thủy thủ đã chết chìm</t>
+          <t>Cetus Kẻ Phá Thủy Triều dẫn dắt những con tàu và thủy thủ đã chìm sâu</t>
         </is>
       </c>
       <c r="N343" t="inlineStr">
@@ -24519,7 +24514,7 @@
       </c>
       <c r="M344" t="inlineStr">
         <is>
-          <t>To the realm beyond</t>
+          <t>Đến cõi bên kia</t>
         </is>
       </c>
       <c r="N344" t="inlineStr">
@@ -24589,7 +24584,7 @@
       </c>
       <c r="M345" t="inlineStr">
         <is>
-          <t>Nhưng chúng thất thường</t>
+          <t>Nhưng chúng lại hay thay đổi</t>
         </is>
       </c>
       <c r="N345" t="inlineStr">
@@ -24659,16 +24654,7 @@
       </c>
       <c r="M346" t="inlineStr">
         <is>
-          <t>Khi chúng cất tiếng hát trong đau buồn và phẫn nộ
-NAME_TITLE_00288:::Bão tố nổi lên
-NAME_TITLE_00289:::Bầu trời tối sầm
-NAME_TITLE_00290:::Cho đến khi Imperator khai sáng chúng bằng ánh đèn lồng
-NAME_TITLE_00291:::Biến chúng thành kẻ thống trị sinh vật biển
-NAME_TITLE_00292:::Và Người Bảo Vệ Biển Cả
-NAME_TITLE_00293:::Vài ngày trước, Ahab triệu tôi đến để nắm lái con tàu tuyệt vời này…
-NAME_TITLE_00294:::Tôi xin lỗi…
-NAME_TITLE_00295:::Bạn đã lạc đường trên biển cả
-NAME_TITLE_00296:::(Kể lại những gì bạn thấy trong phòng học)</t>
+          <t>Khi họ cất tiếng hát trong đau thương và phẫn nộ</t>
         </is>
       </c>
       <c r="N346" t="inlineStr">
@@ -24738,7 +24724,7 @@
       </c>
       <c r="M347" t="inlineStr">
         <is>
-          <t>Tempests raged</t>
+          <t>Bão Tố cuồng nộ</t>
         </is>
       </c>
       <c r="N347" t="inlineStr">
@@ -24808,7 +24794,7 @@
       </c>
       <c r="M348" t="inlineStr">
         <is>
-          <t>Skies darkened</t>
+          <t>Bầu trời tối sầm</t>
         </is>
       </c>
       <c r="N348" t="inlineStr">
@@ -25018,7 +25004,7 @@
       </c>
       <c r="M351" t="inlineStr">
         <is>
-          <t>Và Guardian Biển Cả</t>
+          <t>Và Người Bảo Vệ Biển Cả</t>
         </is>
       </c>
       <c r="N351" t="inlineStr">
@@ -25368,7 +25354,7 @@
       </c>
       <c r="M356" t="inlineStr">
         <is>
-          <t>Cô ấy đã nhắc đến một cái tên—Ciaccona Toccata</t>
+          <t>Cô ấy có nhắc đến một cái tên—Ciaccona Toccata.</t>
         </is>
       </c>
       <c r="N356" t="inlineStr">
@@ -25438,7 +25424,7 @@
       </c>
       <c r="M357" t="inlineStr">
         <is>
-          <t>Tên tôi là Ciaccona, một—</t>
+          <t>Tớ tên là Ciaccona, một…</t>
         </is>
       </c>
       <c r="N357" t="inlineStr">
@@ -25508,7 +25494,7 @@
       </c>
       <c r="M358" t="inlineStr">
         <is>
-          <t>(Không nói gì)</t>
+          <t>(Không nói gì cả)</t>
         </is>
       </c>
       <c r="N358" t="inlineStr">
@@ -25578,7 +25564,7 @@
       </c>
       <c r="M359" t="inlineStr">
         <is>
-          <t>Tôi tin rằng cơ hội đã đến để sự thật được—</t>
+          <t>Tao tin rằng cơ hội để sự thật được phơi bày đã đến...</t>
         </is>
       </c>
       <c r="N359" t="inlineStr">
@@ -25648,7 +25634,7 @@
       </c>
       <c r="M360" t="inlineStr">
         <is>
-          <t>Tôi là làn gió biển dịu dàng,</t>
+          <t>Ta là làn gió biển dịu dàng,</t>
         </is>
       </c>
       <c r="N360" t="inlineStr">
@@ -25788,7 +25774,7 @@
       </c>
       <c r="M362" t="inlineStr">
         <is>
-          <t>Không chỉ vì đã chơi trò chơi cùng tôi, mà còn vì đã giúp tôi nhận ra—</t>
+          <t>Không chỉ là chơi game cùng tớ, mà còn giúp tớ nhận ra—</t>
         </is>
       </c>
       <c r="N362" t="inlineStr">
@@ -25858,7 +25844,7 @@
       </c>
       <c r="M363" t="inlineStr">
         <is>
-          <t>Beep—Simulation over—</t>
+          <t>Bíp—Mô phỏng kết thúc—</t>
         </is>
       </c>
       <c r="N363" t="inlineStr">
@@ -25928,7 +25914,7 @@
       </c>
       <c r="M364" t="inlineStr">
         <is>
-          <t>Vì vậy, tôi muốn hợp tác cùng bạn—</t>
+          <t>Vậy nên, ta muốn kết đội cùng cậu—</t>
         </is>
       </c>
       <c r="N364" t="inlineStr">
@@ -25998,7 +25984,7 @@
       </c>
       <c r="M365" t="inlineStr">
         <is>
-          <t>Abby's Life: Flower Delivery</t>
+          <t>Cuộc sống của Abby: Giao hoa</t>
         </is>
       </c>
       <c r="N365" t="inlineStr">
@@ -26068,7 +26054,7 @@
       </c>
       <c r="M366" t="inlineStr">
         <is>
-          <t>Abby's Life: Cheers</t>
+          <t>Cuộc sống của Abby: Cạn ly nào!</t>
         </is>
       </c>
       <c r="N366" t="inlineStr">
@@ -26138,7 +26124,7 @@
       </c>
       <c r="M367" t="inlineStr">
         <is>
-          <t>Abby's Life: Flower Delivery</t>
+          <t>Cuộc sống của Abby: Giao hoa</t>
         </is>
       </c>
       <c r="N367" t="inlineStr">
@@ -26208,7 +26194,7 @@
       </c>
       <c r="M368" t="inlineStr">
         <is>
-          <t>Abby's Life: Cheers</t>
+          <t>Cuộc sống của Abby: Cạn ly nào!</t>
         </is>
       </c>
       <c r="N368" t="inlineStr">
@@ -26278,7 +26264,7 @@
       </c>
       <c r="M369" t="inlineStr">
         <is>
-          <t>Abby's Life: Flower Delivery</t>
+          <t>Cuộc sống của Abby: Giao hoa</t>
         </is>
       </c>
       <c r="N369" t="inlineStr">
@@ -26348,7 +26334,7 @@
       </c>
       <c r="M370" t="inlineStr">
         <is>
-          <t>Abby's Life: Flower Delivery</t>
+          <t>Cuộc sống của Abby: Giao hoa</t>
         </is>
       </c>
       <c r="N370" t="inlineStr">
@@ -26418,7 +26404,7 @@
       </c>
       <c r="M371" t="inlineStr">
         <is>
-          <t>Abby's Life: Thumbs Up</t>
+          <t>Cuộc sống của Abby: Tán thành!</t>
         </is>
       </c>
       <c r="N371" t="inlineStr">
@@ -26488,7 +26474,7 @@
       </c>
       <c r="M372" t="inlineStr">
         <is>
-          <t>Abby's Life: Thumbs Up</t>
+          <t>Cuộc sống của Abby: Tán thành!</t>
         </is>
       </c>
       <c r="N372" t="inlineStr">
@@ -26558,7 +26544,7 @@
       </c>
       <c r="M373" t="inlineStr">
         <is>
-          <t>Abby's Life: Thumbs Up</t>
+          <t>Cuộc sống của Abby: Tán thành!</t>
         </is>
       </c>
       <c r="N373" t="inlineStr">
@@ -26628,7 +26614,7 @@
       </c>
       <c r="M374" t="inlineStr">
         <is>
-          <t>Abby's Life: Thumbs Up</t>
+          <t>Cuộc sống của Abby: Tán thành!</t>
         </is>
       </c>
       <c r="N374" t="inlineStr">
@@ -26698,7 +26684,7 @@
       </c>
       <c r="M375" t="inlineStr">
         <is>
-          <t>Abby's Life: Shock Solid</t>
+          <t>Cuộc sống của Abby: Điện giật cứng người</t>
         </is>
       </c>
       <c r="N375" t="inlineStr">
@@ -26768,7 +26754,7 @@
       </c>
       <c r="M376" t="inlineStr">
         <is>
-          <t>Abby's Life: Shock Solid</t>
+          <t>Cuộc sống của Abby: Điện giật cứng người</t>
         </is>
       </c>
       <c r="N376" t="inlineStr">
@@ -26838,7 +26824,7 @@
       </c>
       <c r="M377" t="inlineStr">
         <is>
-          <t>Abby's Life: Flower Delivery</t>
+          <t>Cuộc sống của Abby: Giao hoa</t>
         </is>
       </c>
       <c r="N377" t="inlineStr">
@@ -26908,7 +26894,7 @@
       </c>
       <c r="M378" t="inlineStr">
         <is>
-          <t>Abby's Life: Flower Delivery</t>
+          <t>Cuộc sống của Abby: Giao hoa</t>
         </is>
       </c>
       <c r="N378" t="inlineStr">
@@ -26978,7 +26964,7 @@
       </c>
       <c r="M379" t="inlineStr">
         <is>
-          <t>Abby's Life: Shock Solid</t>
+          <t>Cuộc sống của Abby: Điện giật cứng người</t>
         </is>
       </c>
       <c r="N379" t="inlineStr">
@@ -27048,7 +27034,7 @@
       </c>
       <c r="M380" t="inlineStr">
         <is>
-          <t>Abby's Life: Shock Solid</t>
+          <t>Cuộc sống của Abby: Điện giật cứng người</t>
         </is>
       </c>
       <c r="N380" t="inlineStr">
@@ -27748,7 +27734,7 @@
       </c>
       <c r="M390" t="inlineStr">
         <is>
-          <t>Tôi nhớ đêm đó trời đang mưa—</t>
+          <t>Ta nhớ đêm đó trời mưa...</t>
         </is>
       </c>
       <c r="N390" t="inlineStr">
@@ -27958,7 +27944,7 @@
       </c>
       <c r="M393" t="inlineStr">
         <is>
-          <t>Nhưng tôi có hai hộ chiếu ngay đây—</t>
+          <t>Nhưng tớ có hai tấm hộ chiếu ngay đây—</t>
         </is>
       </c>
       <c r="N393" t="inlineStr">
@@ -29638,7 +29624,7 @@
       </c>
       <c r="M417" t="inlineStr">
         <is>
-          <t>(Radio Static)</t>
+          <t>(Tiếng nhiễu sóng vô tuyến)</t>
         </is>
       </c>
       <c r="N417" t="inlineStr">
@@ -29708,7 +29694,7 @@
       </c>
       <c r="M418" t="inlineStr">
         <is>
-          <t>Sender: Ol' Shady</t>
+          <t>Người gửi: Ông Shady</t>
         </is>
       </c>
       <c r="N418" t="inlineStr">
@@ -29778,7 +29764,8 @@
       </c>
       <c r="M419" t="inlineStr">
         <is>
-          <t>[Reply] Sender: Ol' Sunny</t>
+          <t>[
+Trả Lời] Người gửi: Ol' Sunny</t>
         </is>
       </c>
       <c r="N419" t="inlineStr">
@@ -29848,7 +29835,8 @@
       </c>
       <c r="M420" t="inlineStr">
         <is>
-          <t>[Reply] Sender: Ol' Shady</t>
+          <t>[
+Trả Lời] Người gửi: Ol' Shady</t>
         </is>
       </c>
       <c r="N420" t="inlineStr">
@@ -29918,7 +29906,7 @@
       </c>
       <c r="M421" t="inlineStr">
         <is>
-          <t>(Không còn email nào nữa)</t>
+          <t>Không còn email nào nữa.</t>
         </is>
       </c>
       <c r="N421" t="inlineStr">
@@ -32858,7 +32846,7 @@
       </c>
       <c r="M463" t="inlineStr">
         <is>
-          <t>Tớ không ngờ lại hoàn thành thử thách theo cách này…</t>
+          <t>Tôi không ngờ lại hoàn thành thử thách theo cách này…</t>
         </is>
       </c>
       <c r="N463" t="inlineStr">
@@ -33068,7 +33056,7 @@
       </c>
       <c r="M466" t="inlineStr">
         <is>
-          <t>Tớ không định để lộ thân phận, nhưng tên Tuần Tra đó tinh quá…</t>
+          <t>Tôi không định để lộ thân phận đâu, nhưng tên Tuần Tra đó tinh quá…</t>
         </is>
       </c>
       <c r="N466" t="inlineStr">
@@ -33138,7 +33126,7 @@
       </c>
       <c r="M467" t="inlineStr">
         <is>
-          <t>Daddy…</t>
+          <t>Bố ơi…</t>
         </is>
       </c>
       <c r="N467" t="inlineStr">
@@ -33208,7 +33196,7 @@
       </c>
       <c r="M468" t="inlineStr">
         <is>
-          <t>Bố ơi… *khóc*…</t>
+          <t>Bố ơi… *khóc nức nở*…</t>
         </is>
       </c>
       <c r="N468" t="inlineStr">
@@ -33278,7 +33266,7 @@
       </c>
       <c r="M469" t="inlineStr">
         <is>
-          <t>Với Fractsidus xuất hiện, mọi chuyện có thể trở nên tồi tệ rất nhanh…</t>
+          <t>Với Fractsidus xuất hiện, tình hình có thể trở nên tồi tệ rất nhanh…</t>
         </is>
       </c>
       <c r="N469" t="inlineStr">
@@ -33348,7 +33336,7 @@
       </c>
       <c r="M470" t="inlineStr">
         <is>
-          <t>Cậu trông không giống đang thương tiếc ai cả…</t>
+          <t>Anh không tỏ ra đau buồn gì khi mất người ấy à…</t>
         </is>
       </c>
       <c r="N470" t="inlineStr">
@@ -33418,7 +33406,7 @@
       </c>
       <c r="M471" t="inlineStr">
         <is>
-          <t>Tớ cần suy nghĩ kỹ đã…</t>
+          <t>Tôi cần suy xét kỹ càng...</t>
         </is>
       </c>
       <c r="N471" t="inlineStr">
@@ -33488,7 +33476,7 @@
       </c>
       <c r="M472" t="inlineStr">
         <is>
-          <t>Cho tớ thêm chút thời gian…</t>
+          <t>Cho ta thêm chút thời gian thôi…</t>
         </is>
       </c>
       <c r="N472" t="inlineStr">
@@ -33558,7 +33546,7 @@
       </c>
       <c r="M473" t="inlineStr">
         <is>
-          <t>Vậy là cậu vẫn quyết định đi cùng tớ…</t>
+          <t>Vậy là cậu vẫn quyết định đi theo ta…</t>
         </is>
       </c>
       <c r="N473" t="inlineStr">
@@ -33698,7 +33686,7 @@
       </c>
       <c r="M475" t="inlineStr">
         <is>
-          <t>Tôi cần bắt giữ thủ phạm thực sự đứng sau nhóm này…</t>
+          <t>Tôi phải tìm ra thủ phạm thực sự đứng sau nhóm này…</t>
         </is>
       </c>
       <c r="N475" t="inlineStr">
@@ -33768,7 +33756,7 @@
       </c>
       <c r="M476" t="inlineStr">
         <is>
-          <t>Eek… *thở hổn hển*…</t>
+          <t>Ôi… *thở hổn hển*…</t>
         </is>
       </c>
       <c r="N476" t="inlineStr">
@@ -33838,7 +33826,7 @@
       </c>
       <c r="M477" t="inlineStr">
         <is>
-          <t>"Wu Sheng/Shunlian… Lianyue/Lian Xiaosheng… Jinlu/Anh ấy Chang… Lady Guan/Xiaoguan…"</t>
+          <t>"Vũ Sinh/Thuận Liên… Liên Nguyệt/Liên Tiểu Sinh… Kim Lộc/Hà Xương… Quản Nữ/Tiểu Quản…"</t>
         </is>
       </c>
       <c r="N477" t="inlineStr">
@@ -33908,7 +33896,7 @@
       </c>
       <c r="M478" t="inlineStr">
         <is>
-          <t>(Có gì đó ở trong khe hở…)</t>
+          <t>Có gì đó lọt vào khe hở này…</t>
         </is>
       </c>
       <c r="N478" t="inlineStr">
@@ -33978,7 +33966,7 @@
       </c>
       <c r="M479" t="inlineStr">
         <is>
-          <t>Daddy…</t>
+          <t>Bố ơi…</t>
         </is>
       </c>
       <c r="N479" t="inlineStr">
@@ -34048,7 +34036,7 @@
       </c>
       <c r="M480" t="inlineStr">
         <is>
-          <t>Đó là lý do tôi sẽ không để ai đe dọa cuộc sống bình yên của chúng ta nữa…</t>
+          <t>Đó là lý do ta sẽ không để ai đe dọa cuộc sống bình yên của chúng ta lần nữa…</t>
         </is>
       </c>
       <c r="N480" t="inlineStr">
@@ -34118,7 +34106,7 @@
       </c>
       <c r="M481" t="inlineStr">
         <is>
-          <t>Tôi không biết…</t>
+          <t>Tao không biết…</t>
         </is>
       </c>
       <c r="N481" t="inlineStr">
@@ -34188,7 +34176,7 @@
       </c>
       <c r="M482" t="inlineStr">
         <is>
-          <t>Họ không phải người xấu, nhưng…</t>
+          <t>Họ không phải người xấu, nhưng mà…</t>
         </is>
       </c>
       <c r="N482" t="inlineStr">
@@ -34258,7 +34246,7 @@
       </c>
       <c r="M483" t="inlineStr">
         <is>
-          <t>Kindness…</t>
+          <t>Lòng tốt…</t>
         </is>
       </c>
       <c r="N483" t="inlineStr">
@@ -34328,7 +34316,7 @@
       </c>
       <c r="M484" t="inlineStr">
         <is>
-          <t>Giờ thì giao cô gái ra đây…</t>
+          <t>Giờ thì, giao cô gái ra đây…</t>
         </is>
       </c>
       <c r="N484" t="inlineStr">
@@ -34468,7 +34456,7 @@
       </c>
       <c r="M486" t="inlineStr">
         <is>
-          <t>Bao gồm cả những gì đang xảy ra với "Séance Society"…</t>
+          <t>Bao gồm cả tình hình của "Hội Thuyết Linh" nữa…</t>
         </is>
       </c>
       <c r="N486" t="inlineStr">
@@ -34538,7 +34526,7 @@
       </c>
       <c r="M487" t="inlineStr">
         <is>
-          <t>The Fractsidus…</t>
+          <t>Tổ Tacet…</t>
         </is>
       </c>
       <c r="N487" t="inlineStr">
@@ -34608,7 +34596,7 @@
       </c>
       <c r="M488" t="inlineStr">
         <is>
-          <t>Làm ơn nhẹ tay với tôi…</t>
+          <t>Nhẹ tay với tôi thôi nhé...</t>
         </is>
       </c>
       <c r="N488" t="inlineStr">
@@ -34748,7 +34736,7 @@
       </c>
       <c r="M490" t="inlineStr">
         <is>
-          <t>Thế là ổn rồi…</t>
+          <t>Thế là xong...</t>
         </is>
       </c>
       <c r="N490" t="inlineStr">
@@ -34818,7 +34806,7 @@
       </c>
       <c r="M491" t="inlineStr">
         <is>
-          <t>Một số người nói rằng chúng có thể bị thu hút bởi những con rối…</t>
+          <t>Có người còn nói chúng có thể bị thu hút bởi những con rối…</t>
         </is>
       </c>
       <c r="N491" t="inlineStr">
@@ -34888,7 +34876,7 @@
       </c>
       <c r="M492" t="inlineStr">
         <is>
-          <t>Mọi thứ đã trở lại như cũ…</t>
+          <t>Mọi thứ đã trở về chỗ cũ...</t>
         </is>
       </c>
       <c r="N492" t="inlineStr">
